--- a/data/trans_orig/LAWTONB_2R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R3-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>32944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>26117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>54463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67255</t>
+          <t>67764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63674</t>
+          <t>63017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>90653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134358</t>
+          <t>134112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151744</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49147</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>57872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73249</t>
+          <t>73561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102381</t>
+          <t>103056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120066</t>
+          <t>120426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54225</t>
+          <t>54248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48659</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>63079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99460</t>
+          <t>99169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115879</t>
+          <t>115187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>41828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57338</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63402</t>
+          <t>63949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104508</t>
+          <t>104207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23764</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90572</t>
+          <t>90115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101739</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93357</t>
+          <t>93219</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>189241</t>
+          <t>188335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207431</t>
+          <t>207345</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64776</t>
+          <t>63702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85721</t>
+          <t>84530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99858</t>
+          <t>100068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110734</t>
+          <t>110307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130700</t>
+          <t>131343</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>200342</t>
+          <t>201416</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>226846</t>
+          <t>227275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51284</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>164711</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>216682</t>
+          <t>215710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>422082</t>
+          <t>421166</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>451182</t>
+          <t>449662</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>529131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>571200</t>
+          <t>571019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>962626</t>
+          <t>963598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1014597</t>
+          <t>1014316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>17412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32780</t>
+          <t>33099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>50161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>69505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43421</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63623</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53878</t>
+          <t>53558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70589</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58672</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78568</t>
+          <t>79165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117673</t>
+          <t>117952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143521</t>
+          <t>143295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21680</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45513</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34062</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67620</t>
+          <t>67572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90197</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112407</t>
+          <t>112169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>52116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39738</t>
+          <t>40127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54283</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53212</t>
+          <t>52767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70297</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98254</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120464</t>
+          <t>119732</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>29227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>27246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>29553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77429</t>
+          <t>77586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>97310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35476</t>
+          <t>35540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44697</t>
+          <t>45484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44611</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72996</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76787</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96268</t>
+          <t>95229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>96478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118576</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>181230</t>
+          <t>181044</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>209615</t>
+          <t>209448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>41012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97404</t>
+          <t>97421</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113888</t>
+          <t>114058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>125128</t>
+          <t>123405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144320</t>
+          <t>144045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228310</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254242</t>
+          <t>254044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137651</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172810</t>
+          <t>171588</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223623</t>
+          <t>219962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>278494</t>
+          <t>281438</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>421986</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>462199</t>
+          <t>464284</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>519352</t>
+          <t>523013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>570165</t>
+          <t>571387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>959542</t>
+          <t>960424</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1024118</t>
+          <t>1021174</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19330</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68957</t>
+          <t>69054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>40667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50428</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72577</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83199</t>
+          <t>83073</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75065</t>
+          <t>74561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96285</t>
+          <t>95511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152095</t>
+          <t>152243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176319</t>
+          <t>176877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49362</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59530</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61865</t>
+          <t>62368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76045</t>
+          <t>75346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116887</t>
+          <t>116403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132802</t>
+          <t>132766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46066</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>57019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>63905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80894</t>
+          <t>81828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114553</t>
+          <t>113954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135476</t>
+          <t>136280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>39124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60495</t>
+          <t>61193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77606</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29591</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55014</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73101</t>
+          <t>73219</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93336</t>
+          <t>93866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53694</t>
+          <t>53062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48575</t>
+          <t>46301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>74295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84158</t>
+          <t>83913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100251</t>
+          <t>99720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93931</t>
+          <t>94563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117716</t>
+          <t>117829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183443</t>
+          <t>185515</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211235</t>
+          <t>213509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>82,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>61257</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108445</t>
+          <t>107806</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123740</t>
+          <t>124055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>134385</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>157550</t>
+          <t>157003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>250028</t>
+          <t>249208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>277454</t>
+          <t>277064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>160121</t>
+          <t>157849</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>212250</t>
+          <t>210046</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>242771</t>
+          <t>241978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>306347</t>
+          <t>303179</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>485254</t>
+          <t>485103</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>519036</t>
+          <t>517253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>565681</t>
+          <t>567885</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>620082</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1062912</t>
+          <t>1066080</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1126488</t>
+          <t>1127281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25021</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41013</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39909</t>
+          <t>44090</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45095</t>
+          <t>49236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38388</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43572</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>78297</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85939</t>
+          <t>91788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41852</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50079</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>66374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70254</t>
+          <t>77145</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>69895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>86612</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78385</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94507</t>
+          <t>97839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>156867</t>
+          <t>167211</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146678</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166972</t>
+          <t>177217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>45582</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37471</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54383</t>
+          <t>54468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55655</t>
+          <t>54901</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>59730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58781</t>
+          <t>57083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64564</t>
+          <t>63281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>114436</t>
+          <t>111984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105966</t>
+          <t>103098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122878</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>39390</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>32038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44552</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>59345</t>
+          <t>66751</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>71754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>85756</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74335</t>
+          <t>80297</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>91248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>139564</t>
+          <t>152506</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132012</t>
+          <t>143994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146594</t>
+          <t>159858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176564</t>
+          <t>191896</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27315</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40720</t>
+          <t>41569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48155</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>71873</t>
+          <t>75086</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65544</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76459</t>
+          <t>79990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>43324</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36388</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49777</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44658</t>
+          <t>46729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>81789</t>
+          <t>83374</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74946</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88335</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64462</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>124723</t>
+          <t>126698</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96787</t>
+          <t>54221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47777</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>47525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91812</t>
+          <t>70663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>135930</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103263</t>
+          <t>127043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115294</t>
+          <t>141919</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>301821</t>
+          <t>118946</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240772</t>
+          <t>108676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329207</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>412320</t>
+          <t>254876</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>368285</t>
+          <t>242765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>444906</t>
+          <t>265903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>150531</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337559</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>460097</t>
+          <t>313428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>39785</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>133297</t>
+          <t>147640</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127400</t>
+          <t>140798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137489</t>
+          <t>152479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>144477</t>
+          <t>163262</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135716</t>
+          <t>152050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152480</t>
+          <t>172077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>277774</t>
+          <t>310902</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>267748</t>
+          <t>299304</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287347</t>
+          <t>321427</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>330558</t>
+          <t>372735</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>97888</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>130066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123513</t>
+          <t>236056</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>300052</t>
+          <t>274210</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>229064</t>
+          <t>344204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>399571</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>537773</t>
+          <t>596668</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>520783</t>
+          <t>580141</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>551801</t>
+          <t>612319</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>795147</t>
+          <t>642836</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>729172</t>
+          <t>624008</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>905711</t>
+          <t>662162</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1332920</t>
+          <t>1239504</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1274057</t>
+          <t>1212361</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1444564</t>
+          <t>1264220</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
